--- a/agriculture 38.xlsx
+++ b/agriculture 38.xlsx
@@ -202,13 +202,32 @@
     <t xml:space="preserve">2004-05</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Unit:-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Source:Economic and Political Weekly Research Foundation (1950-2019)</t>
   </si>
   <si>
-    <t xml:space="preserve">Source Description:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1962-63 to 2013-14: Plantation Crops: Tea:-&gt; Tea Board India</t>
+    <t xml:space="preserve">Source Description: 1962-63 to 2013-14: Plantation Crops: Tea:-&gt; Tea Board India</t>
   </si>
   <si>
     <t xml:space="preserve">Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
@@ -222,7 +241,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -267,6 +286,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -325,7 +350,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -350,11 +375,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2284,47 +2305,98 @@
         <v>6.31966689830117</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="6"/>
-      <c r="N45" s="6"/>
-      <c r="O45" s="6"/>
-      <c r="P45" s="6"/>
-      <c r="Q45" s="7"/>
-    </row>
-    <row r="46" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+    <row r="45" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="3"/>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="6"/>
+      <c r="O46" s="6"/>
+      <c r="P46" s="6"/>
+      <c r="Q46" s="6"/>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6"/>
+      <c r="P47" s="6"/>
+      <c r="Q47" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6" t="s">
         <v>63</v>
       </c>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="6"/>
+      <c r="O48" s="6"/>
+      <c r="P48" s="6"/>
+      <c r="Q48" s="6"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A45:Q45"/>
+    <mergeCell ref="A46:Q46"/>
+    <mergeCell ref="A47:Q47"/>
+    <mergeCell ref="A48:Q48"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/agriculture 38.xlsx
+++ b/agriculture 38.xlsx
@@ -222,6 +222,16 @@
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Percentage(%)</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Source:Economic and Political Weekly Research Foundation (1950-2019)</t>
@@ -241,7 +251,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -286,12 +296,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -375,7 +379,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/agriculture 38.xlsx
+++ b/agriculture 38.xlsx
@@ -230,7 +230,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Percentage(%)</t>
+      <t xml:space="preserve">Percentage (%)</t>
     </r>
   </si>
   <si>
